--- a/Data/EXCEL/Transfer/salemon/202412/7452-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/7452-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87CE09FA-024B-4537-967D-A09BD13971C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE7BCE1E-28B6-4A45-AA15-FC0714681C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{4E3ED1B6-8B90-4CA1-B2D3-5B5335B8BDED}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{4268A90A-6265-480F-9B71-08C7641B7C61}"/>
   </bookViews>
   <sheets>
     <sheet name="7452-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1258,23 +1258,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A23A4E-293B-402E-A86F-335D4CB7E331}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE6EB2D-361A-4800-B069-F1F8CA85E262}">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" customWidth="1"/>
-    <col min="13" max="13" width="15.26953125" customWidth="1"/>
-    <col min="14" max="15" width="14.54296875" customWidth="1"/>
-    <col min="16" max="16" width="15.26953125" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.625" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="9.625" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1383,7 +1383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45597</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>-16.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45566</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45536</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45505</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45474</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45444</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45413</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>-14.9</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45383</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45352</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>45323</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>-9.75</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45292</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>45261</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45231</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>45200</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>45170</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>45139</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>45108</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>45078</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>45047</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>-7.32</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>45017</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>-4.0599999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44986</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>44958</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44927</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44896</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44866</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>44835</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44805</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>44774</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44743</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>44713</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>44682</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>44652</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>44621</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>44593</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>44562</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>44531</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>44501</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>44470</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>-15.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>44440</v>
       </c>
